--- a/Officiall entries 2.xlsx
+++ b/Officiall entries 2.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Player Events" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Event Analysis" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Rule Violations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="timetable" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -28,12 +29,132 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EC407A"/>
+        <bgColor rgb="00EC407A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFECB3"/>
+        <bgColor rgb="00FFECB3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0066BB6A"/>
+        <bgColor rgb="0066BB6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F48FB1"/>
+        <bgColor rgb="00F48FB1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCA28"/>
+        <bgColor rgb="00FFCA28"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+        <bgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD54F"/>
+        <bgColor rgb="00FFD54F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+        <bgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A5D6A7"/>
+        <bgColor rgb="00A5D6A7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0090CAF9"/>
+        <bgColor rgb="0090CAF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0042A5F5"/>
+        <bgColor rgb="0042A5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE0E0"/>
+        <bgColor rgb="00FDE0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE082"/>
+        <bgColor rgb="00FFE082"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F06292"/>
+        <bgColor rgb="00F06292"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0081C784"/>
+        <bgColor rgb="0081C784"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8BBD0"/>
+        <bgColor rgb="00F8BBD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0064B5F6"/>
+        <bgColor rgb="0064B5F6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -48,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -62,6 +183,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17806,4 +17947,1773 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="G2:CR11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="O2" s="8" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="Q2" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="R2" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="T2" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="U2" s="10" t="inlineStr">
+        <is>
+          <t>WD C - 1</t>
+        </is>
+      </c>
+      <c r="W2" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="X2" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="Y2" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="Z2" s="6" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="AA2" s="6" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="AB2" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AC2" s="13" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="AE2" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AG2" s="10" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="AH2" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AI2" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 1</t>
+        </is>
+      </c>
+      <c r="AJ2" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AK2" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 4</t>
+        </is>
+      </c>
+      <c r="AL2" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AM2" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AN2" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="AO2" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="AP2" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="AQ2" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="AR2" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AS2" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AT2" s="10" t="inlineStr">
+        <is>
+          <t>WD C - 3</t>
+        </is>
+      </c>
+      <c r="AU2" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AV2" s="18" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="AW2" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AX2" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AY2" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="AZ2" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="BA2" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="BB2" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="BC2" s="6" t="inlineStr">
+        <is>
+          <t>XD A - 4</t>
+        </is>
+      </c>
+      <c r="BD2" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BE2" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BF2" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="BG2" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="BH2" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="BI2" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="BJ2" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="BK2" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="BL2" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="BM2" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 4</t>
+        </is>
+      </c>
+      <c r="BN2" s="21" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="BO2" s="21" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="BP2" s="22" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="BQ2" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="BR2" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="BS2" s="18" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="BT2" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 4</t>
+        </is>
+      </c>
+      <c r="BU2" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="BV2" s="23" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="BW2" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="BX2" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 5</t>
+        </is>
+      </c>
+      <c r="BY2" s="24" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="BZ2" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="CA2" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 5</t>
+        </is>
+      </c>
+      <c r="CB2" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="CC2" s="18" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="CE2" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 4</t>
+        </is>
+      </c>
+      <c r="CF2" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 4</t>
+        </is>
+      </c>
+      <c r="CG2" s="24" t="inlineStr">
+        <is>
+          <t>WD A - 3</t>
+        </is>
+      </c>
+      <c r="CI2" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 6</t>
+        </is>
+      </c>
+      <c r="CJ2" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="CK2" s="18" t="inlineStr">
+        <is>
+          <t>WS A - 4</t>
+        </is>
+      </c>
+      <c r="CM2" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 5</t>
+        </is>
+      </c>
+      <c r="CN2" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 5</t>
+        </is>
+      </c>
+      <c r="CO2" s="24" t="inlineStr">
+        <is>
+          <t>WD A - 4</t>
+        </is>
+      </c>
+      <c r="CQ2" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 6</t>
+        </is>
+      </c>
+      <c r="CR2" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="Q3" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="T3" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="U3" s="10" t="inlineStr">
+        <is>
+          <t>WD C - 1</t>
+        </is>
+      </c>
+      <c r="W3" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="Y3" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="AB3" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AC3" s="13" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="AE3" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AG3" s="10" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="AH3" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AJ3" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AK3" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 4</t>
+        </is>
+      </c>
+      <c r="AL3" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AM3" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AN3" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AO3" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="AQ3" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="AS3" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AU3" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AV3" s="18" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="AW3" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AY3" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="BA3" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="BB3" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="BC3" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BD3" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BE3" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BF3" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="BG3" s="23" t="inlineStr">
+        <is>
+          <t>WD B - 1</t>
+        </is>
+      </c>
+      <c r="BH3" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="BI3" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="BJ3" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="BK3" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="BL3" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="BM3" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 4</t>
+        </is>
+      </c>
+      <c r="BN3" s="21" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="BO3" s="21" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="BP3" s="22" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="BQ3" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="BR3" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="BS3" s="18" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="BT3" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="BU3" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="BV3" s="23" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="BW3" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="BX3" s="22" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="BY3" s="24" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="BZ3" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="CA3" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 5</t>
+        </is>
+      </c>
+      <c r="CB3" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="CC3" s="18" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="CE3" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 4</t>
+        </is>
+      </c>
+      <c r="CF3" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 4</t>
+        </is>
+      </c>
+      <c r="CG3" s="24" t="inlineStr">
+        <is>
+          <t>WD A - 3</t>
+        </is>
+      </c>
+      <c r="CI3" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 5</t>
+        </is>
+      </c>
+      <c r="CJ3" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="CM3" s="23" t="inlineStr">
+        <is>
+          <t>WD B - 4</t>
+        </is>
+      </c>
+      <c r="CN3" s="22" t="inlineStr">
+        <is>
+          <t>WD V - 4</t>
+        </is>
+      </c>
+      <c r="CQ3" s="21" t="inlineStr">
+        <is>
+          <t>WS B - 4</t>
+        </is>
+      </c>
+      <c r="CR3" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="T4" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="W4" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="Y4" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="AB4" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AE4" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AH4" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AJ4" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AK4" s="13" t="inlineStr">
+        <is>
+          <t>XD C - 3</t>
+        </is>
+      </c>
+      <c r="AL4" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AM4" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AN4" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AO4" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="AQ4" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="AS4" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AU4" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AW4" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AY4" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="BA4" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="BB4" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="BC4" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BD4" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BE4" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BF4" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="BG4" s="23" t="inlineStr">
+        <is>
+          <t>WD B - 1</t>
+        </is>
+      </c>
+      <c r="BH4" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="BI4" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="BJ4" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="BK4" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="BL4" s="24" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="BM4" s="24" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="BN4" s="21" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="BP4" s="22" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="BR4" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="BS4" s="18" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="BT4" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="BU4" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="BV4" s="23" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="BW4" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="BX4" s="22" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="BZ4" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="CB4" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="CE4" s="23" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="CF4" s="22" t="inlineStr">
+        <is>
+          <t>WD V - 3</t>
+        </is>
+      </c>
+      <c r="CI4" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 5</t>
+        </is>
+      </c>
+      <c r="CJ4" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="CN4" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="Y5" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AA5" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="AB5" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AE5" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AH5" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AJ5" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="AL5" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AN5" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AQ5" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AS5" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AU5" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="AW5" s="18" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="AY5" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="BA5" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="BC5" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BE5" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BG5" s="23" t="inlineStr">
+        <is>
+          <t>WD B - 1</t>
+        </is>
+      </c>
+      <c r="BI5" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="BK5" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="BM5" s="24" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="BN5" s="21" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="BP5" s="22" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="BR5" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="BT5" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="BU5" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="BV5" s="23" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="BX5" s="22" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="BZ5" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="CB5" s="17" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="CE5" s="23" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="CF5" s="22" t="inlineStr">
+        <is>
+          <t>WD V - 3</t>
+        </is>
+      </c>
+      <c r="CI5" s="21" t="inlineStr">
+        <is>
+          <t>WS B - 3</t>
+        </is>
+      </c>
+      <c r="CJ5" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="T6" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="Y6" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AA6" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="AB6" s="12" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AE6" s="9" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="AH6" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AL6" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AN6" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AQ6" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AS6" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AU6" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="AW6" s="18" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="AY6" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="BA6" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="BC6" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BE6" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BI6" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="BK6" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="BM6" s="24" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="BP6" s="22" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="BR6" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="BT6" s="15" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="BV6" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="BX6" s="22" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="BZ6" s="21" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="CB6" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="CF6" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 5</t>
+        </is>
+      </c>
+      <c r="CI6" s="21" t="inlineStr">
+        <is>
+          <t>WS B - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="T7" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="Y7" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="AE7" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AH7" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AL7" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AN7" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AQ7" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AS7" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AU7" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="AW7" s="18" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="AY7" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="BA7" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="BC7" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BE7" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BI7" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="BK7" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="BM7" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 5</t>
+        </is>
+      </c>
+      <c r="BP7" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="BR7" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="BT7" s="18" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="BX7" s="24" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="BZ7" s="21" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="CB7" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="CF7" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="T8" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="Y8" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="AE8" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AH8" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AL8" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AN8" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AQ8" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AS8" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AU8" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="AY8" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="BA8" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="BC8" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BE8" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="BI8" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="BK8" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="BP8" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="BR8" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="BX8" s="24" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="BZ8" s="21" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="CB8" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="Y9" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="AE9" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AH9" s="14" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="AQ9" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AS9" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AU9" s="20" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="AY9" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="BP9" s="16" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="BZ9" s="21" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="CB9" s="19" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="Y10" s="8" t="inlineStr">
+        <is>
+          <t>WS C - 3</t>
+        </is>
+      </c>
+      <c r="AE10" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AQ10" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AS10" s="11" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AY10" s="5" t="inlineStr">
+        <is>
+          <t>XD B - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>